--- a/Result/07-08-25/S&P500stock_07-08-25period252RS90.xlsx
+++ b/Result/07-08-25/S&P500stock_07-08-25period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="129">
   <si>
     <t>Stock</t>
   </si>
@@ -142,199 +142,262 @@
     <t>EM Rating</t>
   </si>
   <si>
+    <t>TKO</t>
+  </si>
+  <si>
     <t>DASH</t>
   </si>
   <si>
+    <t>GEV</t>
+  </si>
+  <si>
+    <t>EQT</t>
+  </si>
+  <si>
     <t>CCL</t>
   </si>
   <si>
+    <t>GILD</t>
+  </si>
+  <si>
     <t>WBD</t>
   </si>
   <si>
-    <t>GLW</t>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>HWM</t>
   </si>
   <si>
     <t>PLTR</t>
   </si>
   <si>
-    <t>APH</t>
-  </si>
-  <si>
-    <t>AVGO</t>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>TPR</t>
   </si>
   <si>
     <t>GE</t>
   </si>
   <si>
-    <t>SCHW</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>HWM</t>
-  </si>
-  <si>
-    <t>SYF</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>TPR</t>
-  </si>
-  <si>
-    <t>C</t>
+    <t>CAH</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>NDAQ</t>
   </si>
   <si>
     <t>BK</t>
   </si>
   <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>EBAY</t>
-  </si>
-  <si>
-    <t>META</t>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>PM</t>
+  </si>
+  <si>
+    <t>PWR</t>
   </si>
   <si>
     <t>GS</t>
   </si>
   <si>
-    <t>RL</t>
-  </si>
-  <si>
     <t>FFIV</t>
   </si>
   <si>
-    <t>PWR</t>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>ORCL</t>
+  </si>
+  <si>
+    <t>VRSN</t>
+  </si>
+  <si>
+    <t>MMM</t>
   </si>
   <si>
     <t>COF</t>
   </si>
   <si>
-    <t>GL</t>
-  </si>
-  <si>
-    <t>ORCL</t>
-  </si>
-  <si>
-    <t>TRMB</t>
+    <t>DRI</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>2025-10-28</t>
-  </si>
-  <si>
-    <t>2025-11-04</t>
-  </si>
-  <si>
-    <t>2025-10-22</t>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>2025-08-07</t>
+  </si>
+  <si>
+    <t>2025-07-23</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
   </si>
   <si>
     <t>2025-09-03</t>
   </si>
   <si>
-    <t>2025-10-14</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>2025-08-05</t>
   </si>
   <si>
     <t>2025-09-24</t>
   </si>
   <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
     <t>2025-08-14</t>
   </si>
   <si>
-    <t>2025-10-10</t>
-  </si>
-  <si>
-    <t>2025-10-30</t>
-  </si>
-  <si>
-    <t>2025-10-24</t>
-  </si>
-  <si>
-    <t>2025-10-23</t>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>2025-08-13</t>
+  </si>
+  <si>
+    <t>2025-07-18</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>2025-07-15</t>
+  </si>
+  <si>
+    <t>2025-07-22</t>
+  </si>
+  <si>
+    <t>2025-07-31</t>
+  </si>
+  <si>
+    <t>2025-07-16</t>
   </si>
   <si>
     <t>2025-09-09</t>
   </si>
   <si>
+    <t>2025-07-25</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
     <t>Consumer Cyclical</t>
   </si>
   <si>
-    <t>Communication Services</t>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
   </si>
   <si>
     <t>Technology</t>
   </si>
   <si>
-    <t>Industrials</t>
+    <t>Utilities</t>
   </si>
   <si>
     <t>Financial Services</t>
   </si>
   <si>
+    <t>Consumer Defensive</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
     <t>Internet Retail</t>
   </si>
   <si>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
     <t>Travel Services</t>
   </si>
   <si>
-    <t>Entertainment</t>
+    <t>Drug Manufacturers - General</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>Software - Infrastructure</t>
   </si>
   <si>
     <t>Electronic Components</t>
   </si>
   <si>
-    <t>Software - Infrastructure</t>
-  </si>
-  <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
+    <t>Utilities - Independent Power Producers</t>
+  </si>
+  <si>
+    <t>Luxury Goods</t>
+  </si>
+  <si>
+    <t>Medical Distribution</t>
+  </si>
+  <si>
+    <t>Financial Data &amp; Stock Exchanges</t>
+  </si>
+  <si>
+    <t>Banks - Diversified</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>Apparel Manufacturing</t>
+  </si>
+  <si>
+    <t>Tobacco</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Construction</t>
   </si>
   <si>
     <t>Capital Markets</t>
   </si>
   <si>
+    <t>Conglomerates</t>
+  </si>
+  <si>
     <t>Credit Services</t>
   </si>
   <si>
-    <t>Luxury Goods</t>
-  </si>
-  <si>
-    <t>Banks - Diversified</t>
-  </si>
-  <si>
-    <t>Computer Hardware</t>
-  </si>
-  <si>
-    <t>Internet Content &amp; Information</t>
-  </si>
-  <si>
-    <t>Apparel Manufacturing</t>
-  </si>
-  <si>
-    <t>Engineering &amp; Construction</t>
-  </si>
-  <si>
-    <t>Insurance - Life</t>
-  </si>
-  <si>
-    <t>Scientific &amp; Technical Instruments</t>
+    <t>Restaurants</t>
   </si>
   <si>
     <t>United States</t>
@@ -695,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AP29"/>
+  <dimension ref="A1:AP32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
@@ -831,124 +894,124 @@
         <v>42</v>
       </c>
       <c r="B2">
-        <v>98.40954274353876</v>
+        <v>95.0199203187251</v>
       </c>
       <c r="C2">
-        <v>95.82504970178927</v>
+        <v>68.32669322709162</v>
       </c>
       <c r="D2">
-        <v>231</v>
+        <v>429</v>
       </c>
       <c r="E2">
-        <v>242</v>
+        <v>411</v>
       </c>
       <c r="F2">
-        <v>258.08</v>
+        <v>176.34</v>
       </c>
       <c r="G2">
-        <v>0.8448824577228047</v>
+        <v>0.4626855356344804</v>
       </c>
       <c r="H2">
-        <v>1.306663357219815</v>
+        <v>0.7829980512151971</v>
       </c>
       <c r="I2">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="J2">
-        <v>-0.3006148608957857</v>
+        <v>-0.0648066400399587</v>
       </c>
       <c r="K2">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>-0.1959565062722765</v>
+        <v>-0.5933956061678015</v>
       </c>
       <c r="M2">
-        <v>253.99599609375</v>
+        <v>177.7</v>
       </c>
       <c r="N2">
-        <v>244.4565002441406</v>
+        <v>172.222501373291</v>
       </c>
       <c r="O2">
-        <v>232.8096997070313</v>
+        <v>166.1666009521484</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2">
-        <v>194.1451251220703</v>
+        <v>147.0868003082275</v>
       </c>
       <c r="R2">
+        <v>1.03</v>
+      </c>
+      <c r="S2">
         <v>1.04</v>
       </c>
-      <c r="S2">
-        <v>1.05</v>
-      </c>
       <c r="U2">
-        <v>5.555555555555555</v>
+        <v>4.444444444444444</v>
       </c>
       <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="b">
         <v>0</v>
       </c>
-      <c r="W2" t="b">
-        <v>1</v>
-      </c>
       <c r="X2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>106.21</v>
+        <v>102.46</v>
       </c>
       <c r="Z2">
-        <v>259.87</v>
+        <v>182.6</v>
       </c>
       <c r="AA2">
-        <v>109.36</v>
+        <v>14.42</v>
       </c>
       <c r="AB2">
-        <v>-1.92</v>
+        <v>-42.28</v>
       </c>
       <c r="AC2">
-        <v>661.77</v>
+        <v>13705.18</v>
       </c>
       <c r="AD2">
-        <v>881.48</v>
+        <v>154.35</v>
       </c>
       <c r="AE2">
-        <v>4.41</v>
+        <v>4.19</v>
       </c>
       <c r="AF2">
-        <v>31.43</v>
+        <v>100</v>
       </c>
       <c r="AG2">
-        <v>-10.26</v>
+        <v>24.14</v>
       </c>
       <c r="AH2">
-        <v>202.63</v>
+        <v>-60.27</v>
       </c>
       <c r="AI2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="AJ2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="AK2" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AL2" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM2">
-        <v>0.79</v>
+        <v>1.97</v>
       </c>
       <c r="AN2">
-        <v>1.78</v>
+        <v>3.24</v>
       </c>
       <c r="AO2">
-        <v>125.32</v>
+        <v>64.47</v>
       </c>
       <c r="AP2">
-        <v>92.85714285714286</v>
+        <v>82.68366090915202</v>
       </c>
     </row>
     <row r="3" spans="1:42">
@@ -956,124 +1019,124 @@
         <v>43</v>
       </c>
       <c r="B3">
-        <v>97.21669980119285</v>
+        <v>99.20318725099602</v>
       </c>
       <c r="C3">
-        <v>97.01789264413519</v>
+        <v>90.63745019920319</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>126</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>164</v>
       </c>
       <c r="F3">
-        <v>29.24</v>
+        <v>246.89</v>
       </c>
       <c r="G3">
-        <v>0.6509798476139294</v>
+        <v>1.144534277224388</v>
       </c>
       <c r="H3">
-        <v>1.807340016374859</v>
+        <v>1.256495469624842</v>
       </c>
       <c r="I3">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="J3">
-        <v>-0.486288745566712</v>
+        <v>0.02068297022551894</v>
       </c>
       <c r="K3">
-        <v>2.57</v>
+        <v>3.01</v>
       </c>
       <c r="L3">
-        <v>1.048806017152811</v>
+        <v>0.5854886850196254</v>
       </c>
       <c r="M3">
-        <v>29.41599998474121</v>
+        <v>241.7999969482422</v>
       </c>
       <c r="N3">
-        <v>29.53450002670288</v>
+        <v>228.8277503967285</v>
       </c>
       <c r="O3">
-        <v>26.9668000793457</v>
+        <v>211.1212994384766</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3">
-        <v>23.92670004844665</v>
+        <v>182.9401749420166</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="S3">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="U3">
+        <v>8.888888888888888</v>
+      </c>
+      <c r="V3" t="b">
         <v>0</v>
       </c>
-      <c r="V3" t="b">
-        <v>1</v>
-      </c>
       <c r="W3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>13.78</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="Z3">
-        <v>31.01</v>
+        <v>248.74</v>
       </c>
       <c r="AA3">
-        <v>39.65</v>
+        <v>104.62</v>
       </c>
       <c r="AB3">
-        <v>-19.76</v>
+        <v>-1.92</v>
       </c>
       <c r="AC3">
-        <v>40.91</v>
+        <v>653.62</v>
       </c>
       <c r="AD3">
-        <v>474.17</v>
+        <v>881.48</v>
       </c>
       <c r="AE3">
-        <v>30.02</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>70</v>
+        <v>4.41</v>
+      </c>
+      <c r="AF3">
+        <v>31.43</v>
+      </c>
+      <c r="AG3">
+        <v>-10.26</v>
+      </c>
+      <c r="AH3">
+        <v>202.63</v>
       </c>
       <c r="AI3" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="AJ3" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AK3" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="AL3" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM3">
-        <v>1.91</v>
+        <v>0.79</v>
       </c>
       <c r="AN3">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AO3">
-        <v>-9.949999999999999</v>
+        <v>125.32</v>
       </c>
       <c r="AP3">
-        <v>57.46762430301249</v>
+        <v>73.27752877658223</v>
       </c>
     </row>
     <row r="4" spans="1:42">
@@ -1081,121 +1144,124 @@
         <v>44</v>
       </c>
       <c r="B4">
-        <v>91.65009940357854</v>
+        <v>99.800796812749</v>
       </c>
       <c r="C4">
-        <v>96.02385685884693</v>
+        <v>98.60557768924303</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>192</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>224</v>
       </c>
       <c r="F4">
-        <v>12.79</v>
+        <v>530.28</v>
       </c>
       <c r="G4">
-        <v>0.2678783706811118</v>
+        <v>1.869329138950441</v>
       </c>
       <c r="H4">
-        <v>1.681408388549289</v>
+        <v>1.802975279264176</v>
       </c>
       <c r="I4">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="J4">
-        <v>-0.04067142235648872</v>
+        <v>0.4196344847977473</v>
       </c>
       <c r="K4">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="L4">
-        <v>0.7048584777853525</v>
+        <v>0.4337511029856002</v>
       </c>
       <c r="M4">
-        <v>12.87000007629394</v>
+        <v>517.5080078125</v>
       </c>
       <c r="N4">
-        <v>12.79850001335144</v>
+        <v>498.0495025634766</v>
       </c>
       <c r="O4">
-        <v>11.41959999084473</v>
+        <v>456.978603515625</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4">
-        <v>10.15344999313355</v>
+        <v>356.4151005554199</v>
       </c>
       <c r="R4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="S4">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="U4">
-        <v>15</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="V4" t="b">
         <v>0</v>
       </c>
       <c r="W4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>6.64</v>
+        <v>150.01</v>
       </c>
       <c r="Z4">
-        <v>13.87</v>
+        <v>532.59</v>
       </c>
       <c r="AA4">
-        <v>31.64</v>
+        <v>144.73</v>
+      </c>
+      <c r="AB4">
+        <v>5.7</v>
       </c>
       <c r="AC4">
-        <v>91.2</v>
+        <v>1167.86</v>
       </c>
       <c r="AD4">
-        <v>53.65</v>
+        <v>293.21</v>
       </c>
       <c r="AE4">
-        <v>-27.69</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>70</v>
+        <v>22.02</v>
+      </c>
+      <c r="AF4">
+        <v>-47.43</v>
+      </c>
+      <c r="AG4">
+        <v>600</v>
+      </c>
+      <c r="AH4">
+        <v>-107.42</v>
       </c>
       <c r="AI4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="AJ4" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="AL4" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM4">
-        <v>-4.4</v>
+        <v>6.98</v>
       </c>
       <c r="AN4">
-        <v>-0.13</v>
+        <v>6.9</v>
       </c>
       <c r="AO4">
-        <v>97.05</v>
+        <v>-1.15</v>
       </c>
       <c r="AP4">
-        <v>56.77293330356576</v>
+        <v>73.26427581640704</v>
       </c>
     </row>
     <row r="5" spans="1:42">
@@ -1203,124 +1269,121 @@
         <v>45</v>
       </c>
       <c r="B5">
-        <v>94.43339960238568</v>
+        <v>91.63346613545816</v>
       </c>
       <c r="C5">
-        <v>96.22266401590457</v>
+        <v>53.78486055776892</v>
       </c>
       <c r="D5">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="E5">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="F5">
-        <v>63.98</v>
+        <v>56.16</v>
       </c>
       <c r="G5">
-        <v>0.4346622880305219</v>
+        <v>0.4029185836750009</v>
       </c>
       <c r="H5">
-        <v>1.187691770150619</v>
+        <v>0.8752472688168852</v>
       </c>
       <c r="I5">
-        <v>2.92</v>
+        <v>2.09</v>
       </c>
       <c r="J5">
-        <v>1.184776216471626</v>
+        <v>0.3626414112874289</v>
       </c>
       <c r="K5">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="L5">
-        <v>0.0660987618172155</v>
+        <v>-0.406641659049001</v>
       </c>
       <c r="M5">
-        <v>63.18600006103516</v>
+        <v>56.33000030517578</v>
       </c>
       <c r="N5">
-        <v>57.07049999237061</v>
+        <v>57.2125</v>
       </c>
       <c r="O5">
-        <v>53.49539985656738</v>
+        <v>55.43120018005371</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5">
-        <v>49.0459499168396</v>
+        <v>48.12155012130737</v>
       </c>
       <c r="R5">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="S5">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
       </c>
       <c r="W5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>37.18</v>
+        <v>30.02</v>
       </c>
       <c r="Z5">
-        <v>64.41</v>
+        <v>61.02</v>
       </c>
       <c r="AA5">
-        <v>54.81</v>
-      </c>
-      <c r="AB5">
-        <v>-11.42</v>
+        <v>33.62</v>
       </c>
       <c r="AC5">
-        <v>26.17</v>
+        <v>108.94</v>
       </c>
       <c r="AD5">
-        <v>350.33</v>
+        <v>72.55</v>
       </c>
       <c r="AE5">
-        <v>7.55</v>
+        <v>2.06</v>
       </c>
       <c r="AF5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AG5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="AJ5" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="AL5" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM5">
-        <v>0.9399999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="AN5">
-        <v>2.31</v>
+        <v>2.52</v>
       </c>
       <c r="AO5">
-        <v>145.74</v>
+        <v>313.11</v>
       </c>
       <c r="AP5">
-        <v>50.81151301405418</v>
+        <v>45.90877473842633</v>
       </c>
     </row>
     <row r="6" spans="1:42">
@@ -1328,58 +1391,58 @@
         <v>46</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>96.61354581673307</v>
       </c>
       <c r="C6">
-        <v>98.40954274353876</v>
+        <v>97.41035856573706</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>179.54</v>
+        <v>29.31</v>
       </c>
       <c r="G6">
-        <v>6.009632480173214</v>
+        <v>0.4784299555356603</v>
       </c>
       <c r="H6">
-        <v>2.136553413893573</v>
+        <v>1.79953212396498</v>
       </c>
       <c r="I6">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="J6">
-        <v>0.8258067061078346</v>
+        <v>1.630737296892013</v>
       </c>
       <c r="K6">
-        <v>3.16</v>
+        <v>3.7</v>
       </c>
       <c r="L6">
-        <v>2.015134818232814</v>
+        <v>1.390865081969452</v>
       </c>
       <c r="M6">
-        <v>165.2180023193359</v>
+        <v>29.13599967956543</v>
       </c>
       <c r="N6">
-        <v>155.4360023498535</v>
+        <v>25.58400011062622</v>
       </c>
       <c r="O6">
-        <v>142.8004006958008</v>
+        <v>23.15740005493164</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6">
-        <v>98.52420017242432</v>
+        <v>22.77360005378723</v>
       </c>
       <c r="R6">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="S6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -1391,61 +1454,61 @@
         <v>1</v>
       </c>
       <c r="X6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>21.23</v>
+        <v>13.78</v>
       </c>
       <c r="Z6">
-        <v>180.58</v>
+        <v>30.46</v>
       </c>
       <c r="AA6">
-        <v>425.93</v>
+        <v>39.74</v>
       </c>
       <c r="AB6">
-        <v>-73.95999999999999</v>
+        <v>-19.76</v>
       </c>
       <c r="AC6">
-        <v>55.28</v>
+        <v>39.57</v>
       </c>
       <c r="AD6">
-        <v>129.32</v>
+        <v>474.17</v>
       </c>
       <c r="AE6">
-        <v>15.3</v>
-      </c>
-      <c r="AF6">
-        <v>125</v>
-      </c>
-      <c r="AG6">
-        <v>-33.33</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
+        <v>30.02</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>75</v>
       </c>
       <c r="AI6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AK6" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="AL6" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM6">
-        <v>0.29</v>
+        <v>1.91</v>
       </c>
       <c r="AN6">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="AO6">
-        <v>62.07</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="AP6">
-        <v>50.6542011353657</v>
+        <v>45.81406718235551</v>
       </c>
     </row>
     <row r="7" spans="1:42">
@@ -1453,64 +1516,64 @@
         <v>47</v>
       </c>
       <c r="B7">
-        <v>96.62027833001989</v>
+        <v>95.61752988047809</v>
       </c>
       <c r="C7">
-        <v>94.83101391650099</v>
+        <v>29.28286852589641</v>
       </c>
       <c r="D7">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="E7">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F7">
-        <v>109.5</v>
+        <v>111.78</v>
       </c>
       <c r="G7">
-        <v>0.5834122648509167</v>
+        <v>0.6171478110456752</v>
       </c>
       <c r="H7">
-        <v>1.35409389674877</v>
+        <v>0.3308730852535074</v>
       </c>
       <c r="I7">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="J7">
-        <v>-0.4243974506764031</v>
+        <v>-0.4067650811018689</v>
       </c>
       <c r="K7">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="L7">
-        <v>-0.9821223105407531</v>
+        <v>-0.5233628759982513</v>
       </c>
       <c r="M7">
-        <v>107.3759994506836</v>
+        <v>111.5280014038086</v>
       </c>
       <c r="N7">
-        <v>103.6314990997314</v>
+        <v>109.8730007171631</v>
       </c>
       <c r="O7">
-        <v>97.95719955444336</v>
+        <v>106.9094003295898</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7">
-        <v>77.66814975738525</v>
+        <v>99.16929996490478</v>
       </c>
       <c r="R7">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="S7">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="U7">
         <v>0</v>
       </c>
       <c r="V7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="b">
         <v>1</v>
@@ -1519,58 +1582,58 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>54.77</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="Z7">
-        <v>109.9</v>
+        <v>119.96</v>
       </c>
       <c r="AA7">
-        <v>133.69</v>
+        <v>139.05</v>
       </c>
       <c r="AB7">
-        <v>15.39</v>
+        <v>-38.13</v>
       </c>
       <c r="AC7">
-        <v>60.04</v>
+        <v>72.52</v>
       </c>
       <c r="AD7">
-        <v>106.75</v>
+        <v>131.24</v>
       </c>
       <c r="AE7">
-        <v>31.02</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>70</v>
+        <v>32.51</v>
+      </c>
+      <c r="AF7">
+        <v>-25.87</v>
+      </c>
+      <c r="AG7">
+        <v>43</v>
+      </c>
+      <c r="AH7">
+        <v>-22.48</v>
       </c>
       <c r="AI7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="AJ7" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="AL7" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM7">
-        <v>2.51</v>
+        <v>4.76</v>
       </c>
       <c r="AN7">
-        <v>2.16</v>
+        <v>7.43</v>
       </c>
       <c r="AO7">
-        <v>-13.94</v>
+        <v>56.09</v>
       </c>
       <c r="AP7">
-        <v>50.03437765954446</v>
+        <v>42.90604256693177</v>
       </c>
     </row>
     <row r="8" spans="1:42">
@@ -1578,124 +1641,121 @@
         <v>48</v>
       </c>
       <c r="B8">
-        <v>98.01192842942345</v>
+        <v>92.62948207171314</v>
       </c>
       <c r="C8">
-        <v>97.21669980119285</v>
+        <v>85.85657370517929</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>301.67</v>
+        <v>11.02</v>
       </c>
       <c r="G8">
-        <v>0.7139182386793264</v>
+        <v>0.3410770842266375</v>
       </c>
       <c r="H8">
-        <v>1.961132318941561</v>
+        <v>1.609323424772671</v>
       </c>
       <c r="I8">
-        <v>1.87</v>
+        <v>2.95</v>
       </c>
       <c r="J8">
-        <v>-0.1149409762248591</v>
+        <v>1.587992491759274</v>
       </c>
       <c r="K8">
-        <v>2.09</v>
+        <v>3.95</v>
       </c>
       <c r="L8">
-        <v>0.2626402128843344</v>
+        <v>1.682668124342578</v>
       </c>
       <c r="M8">
-        <v>294.9320068359375</v>
+        <v>11.15200004577637</v>
       </c>
       <c r="N8">
-        <v>287.7650009155274</v>
+        <v>10.65749998092651</v>
       </c>
       <c r="O8">
-        <v>269.3657992553711</v>
+        <v>9.738400020599364</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8">
-        <v>216.2870995330811</v>
+        <v>9.639749982357024</v>
       </c>
       <c r="R8">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="S8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="U8">
-        <v>2.777777777777778</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="V8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>128.5</v>
+        <v>6.64</v>
       </c>
       <c r="Z8">
-        <v>306.95</v>
+        <v>12.7</v>
       </c>
       <c r="AA8">
-        <v>1418.9</v>
-      </c>
-      <c r="AB8">
-        <v>13.91</v>
+        <v>27.26</v>
       </c>
       <c r="AC8">
-        <v>35.81</v>
+        <v>91.25</v>
       </c>
       <c r="AD8">
-        <v>132.81</v>
+        <v>53.65</v>
       </c>
       <c r="AE8">
-        <v>18.98</v>
-      </c>
-      <c r="AF8">
-        <v>26.62</v>
-      </c>
-      <c r="AG8">
-        <v>331</v>
-      </c>
-      <c r="AH8">
-        <v>-187.72</v>
+        <v>-27.69</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>75</v>
       </c>
       <c r="AI8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AJ8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="AK8" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="AL8" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM8">
-        <v>2.75</v>
+        <v>-4.4</v>
       </c>
       <c r="AN8">
-        <v>6.17</v>
+        <v>-0.13</v>
       </c>
       <c r="AO8">
-        <v>124.36</v>
+        <v>97.05</v>
       </c>
       <c r="AP8">
-        <v>48.00012368643522</v>
+        <v>40.18158832720728</v>
       </c>
     </row>
     <row r="9" spans="1:42">
@@ -1703,64 +1763,64 @@
         <v>49</v>
       </c>
       <c r="B9">
-        <v>95.62624254473161</v>
+        <v>96.41434262948208</v>
       </c>
       <c r="C9">
-        <v>89.66202783300199</v>
+        <v>97.60956175298804</v>
       </c>
       <c r="D9">
-        <v>210</v>
+        <v>26</v>
       </c>
       <c r="E9">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>272.28</v>
+        <v>274.18</v>
       </c>
       <c r="G9">
-        <v>0.4681843483430091</v>
+        <v>0.3613274301394256</v>
       </c>
       <c r="H9">
-        <v>1.143569389310801</v>
+        <v>2.041431682661473</v>
       </c>
       <c r="I9">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="J9">
-        <v>-0.7586104430840707</v>
+        <v>0.6618550472166003</v>
       </c>
       <c r="K9">
-        <v>1.48</v>
+        <v>3.43</v>
       </c>
       <c r="L9">
-        <v>-0.7364454967068542</v>
+        <v>1.075717796206477</v>
       </c>
       <c r="M9">
-        <v>272.2179992675781</v>
+        <v>271.9299926757812</v>
       </c>
       <c r="N9">
-        <v>266.2464973449707</v>
+        <v>258.8799987792969</v>
       </c>
       <c r="O9">
-        <v>254.2867993164062</v>
+        <v>236.821598815918</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9">
-        <v>206.8995999145508</v>
+        <v>203.9617995452881</v>
       </c>
       <c r="R9">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="S9">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="U9">
-        <v>16.66666666666666</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="V9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="b">
         <v>1</v>
@@ -1769,58 +1829,58 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>150.2</v>
+        <v>128.5</v>
       </c>
       <c r="Z9">
-        <v>277</v>
+        <v>277.71</v>
       </c>
       <c r="AA9">
-        <v>288.74</v>
+        <v>1289.6</v>
       </c>
       <c r="AB9">
-        <v>94.19</v>
+        <v>13.91</v>
       </c>
       <c r="AC9">
-        <v>27.61</v>
+        <v>35.67</v>
       </c>
       <c r="AD9">
-        <v>65.70999999999999</v>
+        <v>132.81</v>
       </c>
       <c r="AE9">
-        <v>40.2</v>
+        <v>18.98</v>
       </c>
       <c r="AF9">
-        <v>5.11</v>
+        <v>26.62</v>
       </c>
       <c r="AG9">
-        <v>2.92</v>
+        <v>331</v>
       </c>
       <c r="AH9">
-        <v>47.41</v>
+        <v>-187.72</v>
       </c>
       <c r="AI9" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="AK9" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="AL9" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM9">
-        <v>7.02</v>
+        <v>2.75</v>
       </c>
       <c r="AN9">
-        <v>5.24</v>
+        <v>6.17</v>
       </c>
       <c r="AO9">
-        <v>-25.36</v>
+        <v>124.36</v>
       </c>
       <c r="AP9">
-        <v>47.33494359148194</v>
+        <v>39.52996372750908</v>
       </c>
     </row>
     <row r="10" spans="1:42">
@@ -1828,124 +1888,127 @@
         <v>50</v>
       </c>
       <c r="B10">
-        <v>90.4572564612326</v>
+        <v>98.60557768924303</v>
       </c>
       <c r="C10">
-        <v>75.14910536779324</v>
+        <v>98.00796812749005</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="E10">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="F10">
-        <v>96.70999999999999</v>
+        <v>328.85</v>
       </c>
       <c r="G10">
-        <v>0.3581860520085017</v>
+        <v>0.9303133957038727</v>
       </c>
       <c r="H10">
-        <v>0.8499149482674864</v>
+        <v>1.640675382837682</v>
       </c>
       <c r="I10">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="J10">
-        <v>-0.8947712918427502</v>
+        <v>0.3198966061546903</v>
       </c>
       <c r="K10">
-        <v>0.96</v>
+        <v>3.1</v>
       </c>
       <c r="L10">
-        <v>-1.588125117997704</v>
+        <v>0.690537780273951</v>
       </c>
       <c r="M10">
-        <v>96.70200042724609</v>
+        <v>323.5340087890625</v>
       </c>
       <c r="N10">
-        <v>95.38650054931641</v>
+        <v>287.0305023193359</v>
       </c>
       <c r="O10">
-        <v>91.72800018310546</v>
+        <v>259.2140002441406</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10">
-        <v>81.75295024871826</v>
+        <v>230.7794500732422</v>
       </c>
       <c r="R10">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="S10">
-        <v>1.04</v>
+        <v>1.11</v>
+      </c>
+      <c r="T10" t="s">
+        <v>19</v>
       </c>
       <c r="U10">
-        <v>4.444444444444444</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="V10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>61.15</v>
+        <v>130.08</v>
       </c>
       <c r="Z10">
-        <v>99.59</v>
+        <v>336.59</v>
       </c>
       <c r="AA10">
-        <v>175.72</v>
+        <v>89.3</v>
       </c>
       <c r="AB10">
-        <v>2.26</v>
+        <v>4.1</v>
       </c>
       <c r="AC10">
-        <v>42.72</v>
+        <v>30.43</v>
       </c>
       <c r="AD10">
-        <v>64.33</v>
+        <v>106.46</v>
       </c>
       <c r="AE10">
-        <v>15.59</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>70</v>
+        <v>49.55</v>
+      </c>
+      <c r="AF10">
+        <v>31.55</v>
+      </c>
+      <c r="AG10">
+        <v>-51.18</v>
+      </c>
+      <c r="AH10">
+        <v>27.11</v>
       </c>
       <c r="AI10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AJ10" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AK10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="AL10" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM10">
-        <v>3.72</v>
+        <v>12.28</v>
       </c>
       <c r="AN10">
-        <v>3.8</v>
+        <v>14.29</v>
       </c>
       <c r="AO10">
-        <v>2.15</v>
+        <v>16.37</v>
       </c>
       <c r="AP10">
-        <v>45.16842391588968</v>
+        <v>39.23818180450732</v>
       </c>
     </row>
     <row r="11" spans="1:42">
@@ -1953,124 +2016,124 @@
         <v>51</v>
       </c>
       <c r="B11">
-        <v>99.00596421471172</v>
+        <v>99.40239043824701</v>
       </c>
       <c r="C11">
-        <v>94.63220675944333</v>
+        <v>94.02390438247012</v>
       </c>
       <c r="D11">
-        <v>308</v>
+        <v>169</v>
       </c>
       <c r="E11">
-        <v>296</v>
+        <v>174</v>
       </c>
       <c r="F11">
-        <v>314.02</v>
+        <v>180.25</v>
       </c>
       <c r="G11">
-        <v>0.9020384091141131</v>
+        <v>1.117074773471908</v>
       </c>
       <c r="H11">
-        <v>1.626783166493569</v>
+        <v>1.314545600597227</v>
       </c>
       <c r="I11">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="J11">
-        <v>-0.1396974941809826</v>
+        <v>0.2059104591340535</v>
       </c>
       <c r="K11">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="L11">
-        <v>0.295397121395521</v>
+        <v>-0.1265107383708008</v>
       </c>
       <c r="M11">
-        <v>314.6399963378906</v>
+        <v>179.9220001220703</v>
       </c>
       <c r="N11">
-        <v>337.0879989624024</v>
+        <v>175.3625</v>
       </c>
       <c r="O11">
-        <v>304.5924011230469</v>
+        <v>165.368200378418</v>
       </c>
       <c r="P11" t="b">
         <v>1</v>
       </c>
       <c r="Q11">
-        <v>247.8049501037598</v>
+        <v>129.3092501831055</v>
       </c>
       <c r="R11">
-        <v>0.93</v>
+        <v>1.03</v>
       </c>
       <c r="S11">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="U11">
-        <v>14.44444444444444</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="V11" t="b">
         <v>0</v>
       </c>
       <c r="W11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>130.08</v>
+        <v>77.22</v>
       </c>
       <c r="Z11">
-        <v>355.91</v>
+        <v>187.51</v>
       </c>
       <c r="AA11">
-        <v>85.3</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="AB11">
-        <v>4.1</v>
+        <v>22.24</v>
       </c>
       <c r="AC11">
-        <v>32.34</v>
+        <v>30.78</v>
       </c>
       <c r="AD11">
-        <v>44.78</v>
+        <v>43.48</v>
       </c>
       <c r="AE11">
-        <v>47.48</v>
+        <v>28.29</v>
       </c>
       <c r="AF11">
-        <v>31.55</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AG11">
-        <v>-51.18</v>
+        <v>-3.7</v>
       </c>
       <c r="AH11">
-        <v>27.11</v>
+        <v>24.62</v>
       </c>
       <c r="AI11" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AJ11" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="AK11" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="AL11" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM11">
-        <v>13.45</v>
+        <v>3.06</v>
       </c>
       <c r="AN11">
-        <v>14.29</v>
+        <v>3.17</v>
       </c>
       <c r="AO11">
-        <v>6.25</v>
+        <v>3.59</v>
       </c>
       <c r="AP11">
-        <v>44.88697090277776</v>
+        <v>37.29692082542022</v>
       </c>
     </row>
     <row r="12" spans="1:42">
@@ -2078,124 +2141,124 @@
         <v>52</v>
       </c>
       <c r="B12">
-        <v>97.4155069582505</v>
+        <v>100</v>
       </c>
       <c r="C12">
-        <v>77.73359840954275</v>
+        <v>97.80876494023904</v>
       </c>
       <c r="D12">
-        <v>184</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>235</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>182.06</v>
+        <v>139.12</v>
       </c>
       <c r="G12">
-        <v>0.8170491864670195</v>
+        <v>4.147082579127334</v>
       </c>
       <c r="H12">
-        <v>1.300926007008828</v>
+        <v>2.151703561746393</v>
       </c>
       <c r="I12">
-        <v>2.13</v>
+        <v>3.41</v>
       </c>
       <c r="J12">
-        <v>0.2068937572047465</v>
+        <v>2.243412837127936</v>
       </c>
       <c r="K12">
-        <v>1.76</v>
+        <v>4.65</v>
       </c>
       <c r="L12">
-        <v>-0.2778487775502429</v>
+        <v>2.499716642987329</v>
       </c>
       <c r="M12">
-        <v>181.3140014648438</v>
+        <v>134.5199981689453</v>
       </c>
       <c r="N12">
-        <v>185.0385002136231</v>
+        <v>136.6039993286133</v>
       </c>
       <c r="O12">
-        <v>178.8620001220703</v>
+        <v>127.8141995239258</v>
       </c>
       <c r="P12" t="b">
         <v>1</v>
       </c>
       <c r="Q12">
-        <v>138.5531002807617</v>
+        <v>85.87354991912842</v>
       </c>
       <c r="R12">
         <v>0.98</v>
       </c>
       <c r="S12">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="U12">
-        <v>8.888888888888889</v>
+        <v>0</v>
       </c>
       <c r="V12" t="b">
         <v>0</v>
       </c>
       <c r="W12" t="b">
+        <v>1</v>
+      </c>
+      <c r="X12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>21.23</v>
+      </c>
+      <c r="Z12">
+        <v>148.21</v>
+      </c>
+      <c r="AA12">
+        <v>328.31</v>
+      </c>
+      <c r="AB12">
+        <v>-73.95999999999999</v>
+      </c>
+      <c r="AC12">
+        <v>41.81</v>
+      </c>
+      <c r="AD12">
+        <v>90.45</v>
+      </c>
+      <c r="AE12">
+        <v>12.41</v>
+      </c>
+      <c r="AF12">
+        <v>125</v>
+      </c>
+      <c r="AG12">
+        <v>-33.33</v>
+      </c>
+      <c r="AH12">
         <v>0</v>
       </c>
-      <c r="X12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>85.39</v>
-      </c>
-      <c r="Z12">
-        <v>193.26</v>
-      </c>
-      <c r="AA12">
-        <v>73.39</v>
-      </c>
-      <c r="AB12">
-        <v>22.24</v>
-      </c>
-      <c r="AC12">
-        <v>33.83</v>
-      </c>
-      <c r="AD12">
-        <v>54.9</v>
-      </c>
-      <c r="AE12">
-        <v>29.98</v>
-      </c>
-      <c r="AF12">
-        <v>8.970000000000001</v>
-      </c>
-      <c r="AG12">
-        <v>-3.7</v>
-      </c>
-      <c r="AH12">
-        <v>24.62</v>
-      </c>
       <c r="AI12" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="AJ12" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AL12" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM12">
-        <v>3.43</v>
+        <v>0.23</v>
       </c>
       <c r="AN12">
-        <v>3.17</v>
+        <v>0.47</v>
       </c>
       <c r="AO12">
-        <v>-7.58</v>
+        <v>104.35</v>
       </c>
       <c r="AP12">
-        <v>43.98177564076499</v>
+        <v>37.08120862427899</v>
       </c>
     </row>
     <row r="13" spans="1:42">
@@ -2203,124 +2266,127 @@
         <v>53</v>
       </c>
       <c r="B13">
-        <v>91.45129224652088</v>
+        <v>98.40637450199203</v>
       </c>
       <c r="C13">
-        <v>87.27634194831015</v>
+        <v>99.00398406374502</v>
       </c>
       <c r="D13">
-        <v>202</v>
+        <v>343</v>
       </c>
       <c r="E13">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="F13">
-        <v>69.45</v>
+        <v>225.41</v>
       </c>
       <c r="G13">
-        <v>0.2371582927497619</v>
+        <v>0.8853399426750777</v>
       </c>
       <c r="H13">
-        <v>1.652077374996477</v>
+        <v>1.387075767070799</v>
       </c>
       <c r="I13">
-        <v>1.65</v>
+        <v>2.21</v>
       </c>
       <c r="J13">
-        <v>-0.3872626737422181</v>
+        <v>0.5336206318183842</v>
       </c>
       <c r="K13">
-        <v>1.98</v>
+        <v>2.64</v>
       </c>
       <c r="L13">
-        <v>0.08247721607280876</v>
+        <v>0.1536201823074</v>
       </c>
       <c r="M13">
-        <v>69.17799835205078</v>
+        <v>221.5100006103516</v>
       </c>
       <c r="N13">
-        <v>70.39650039672851</v>
+        <v>201.4574996948242</v>
       </c>
       <c r="O13">
-        <v>65.82960037231446</v>
+        <v>176.8179998779297</v>
       </c>
       <c r="P13" t="b">
         <v>1</v>
       </c>
       <c r="Q13">
-        <v>61.48145004272461</v>
+        <v>148.5414999389648</v>
       </c>
       <c r="R13">
-        <v>0.98</v>
+        <v>1.1</v>
       </c>
       <c r="S13">
-        <v>1.07</v>
+        <v>1.14</v>
+      </c>
+      <c r="T13" t="s">
+        <v>73</v>
       </c>
       <c r="U13">
-        <v>7.777777777777777</v>
+        <v>17.77777777777778</v>
       </c>
       <c r="V13" t="b">
         <v>0</v>
       </c>
       <c r="W13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>40.54</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="Z13">
-        <v>73.76000000000001</v>
+        <v>227.54</v>
       </c>
       <c r="AA13">
-        <v>25.84</v>
+        <v>24.19</v>
       </c>
       <c r="AB13">
-        <v>8.99</v>
+        <v>43.9</v>
       </c>
       <c r="AC13">
-        <v>31.12</v>
+        <v>10.19</v>
       </c>
       <c r="AD13">
-        <v>61</v>
+        <v>91.61</v>
       </c>
       <c r="AE13">
-        <v>20.23</v>
+        <v>32.41</v>
       </c>
       <c r="AF13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AG13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ13" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AL13" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM13">
-        <v>8.23</v>
+        <v>5.24</v>
       </c>
       <c r="AN13">
-        <v>6.47</v>
+        <v>10.01</v>
       </c>
       <c r="AO13">
-        <v>-21.39</v>
+        <v>91.03</v>
       </c>
       <c r="AP13">
-        <v>43.37685436665609</v>
+        <v>36.90012956220631</v>
       </c>
     </row>
     <row r="14" spans="1:42">
@@ -2328,58 +2394,58 @@
         <v>54</v>
       </c>
       <c r="B14">
-        <v>98.80715705765407</v>
+        <v>98.20717131474103</v>
       </c>
       <c r="C14">
-        <v>96.62027833001989</v>
+        <v>98.40637450199203</v>
       </c>
       <c r="D14">
-        <v>426</v>
+        <v>243</v>
       </c>
       <c r="E14">
-        <v>401</v>
+        <v>216</v>
       </c>
       <c r="F14">
-        <v>220.68</v>
+        <v>158.69</v>
       </c>
       <c r="G14">
-        <v>0.9702612702879198</v>
+        <v>0.8074604347432857</v>
       </c>
       <c r="H14">
-        <v>1.354374181763625</v>
+        <v>1.68839062535224</v>
       </c>
       <c r="I14">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J14">
-        <v>-0.1025627172467976</v>
+        <v>0.04917950698067815</v>
       </c>
       <c r="K14">
-        <v>1.98</v>
+        <v>4.25</v>
       </c>
       <c r="L14">
-        <v>0.08247721607280876</v>
+        <v>2.032831775190328</v>
       </c>
       <c r="M14">
-        <v>220.8619964599609</v>
+        <v>157.8320007324219</v>
       </c>
       <c r="N14">
-        <v>222.3414985656738</v>
+        <v>154.7389999389648</v>
       </c>
       <c r="O14">
-        <v>205.5637994384766</v>
+        <v>145.6154000854492</v>
       </c>
       <c r="P14" t="b">
         <v>1</v>
       </c>
       <c r="Q14">
-        <v>159.9010496902466</v>
+        <v>108.3247001647949</v>
       </c>
       <c r="R14">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="S14">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="U14">
         <v>19.44444444444445</v>
@@ -2388,64 +2454,64 @@
         <v>0</v>
       </c>
       <c r="W14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>95.84999999999999</v>
+        <v>65.11</v>
       </c>
       <c r="Z14">
-        <v>232.84</v>
+        <v>168.57</v>
       </c>
       <c r="AA14">
-        <v>23.68</v>
+        <v>31.03</v>
       </c>
       <c r="AB14">
-        <v>43.9</v>
+        <v>-20.43</v>
       </c>
       <c r="AC14">
-        <v>10.37</v>
+        <v>12.41</v>
       </c>
       <c r="AD14">
-        <v>91.61</v>
+        <v>56.42</v>
       </c>
       <c r="AE14">
-        <v>32.41</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>70</v>
+        <v>44.91</v>
+      </c>
+      <c r="AF14">
+        <v>19.35</v>
+      </c>
+      <c r="AG14">
+        <v>181.79</v>
+      </c>
+      <c r="AH14">
+        <v>-209.22</v>
       </c>
       <c r="AI14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="AK14" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="AL14" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM14">
-        <v>5.25</v>
+        <v>6.29</v>
       </c>
       <c r="AN14">
-        <v>10.01</v>
+        <v>6.9</v>
       </c>
       <c r="AO14">
-        <v>90.67</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AP14">
-        <v>41.93732432039526</v>
+        <v>36.38201481946785</v>
       </c>
     </row>
     <row r="15" spans="1:42">
@@ -2453,64 +2519,64 @@
         <v>55</v>
       </c>
       <c r="B15">
-        <v>95.22862823061629</v>
+        <v>99.00398406374502</v>
       </c>
       <c r="C15">
-        <v>98.60834990059642</v>
+        <v>92.43027888446214</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>168</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="F15">
-        <v>179.42</v>
+        <v>92.47</v>
       </c>
       <c r="G15">
-        <v>0.3564840462194169</v>
+        <v>1.152537174492341</v>
       </c>
       <c r="H15">
-        <v>2.066374801041833</v>
+        <v>1.243127761112169</v>
       </c>
       <c r="I15">
-        <v>1.74</v>
+        <v>2.31</v>
       </c>
       <c r="J15">
-        <v>-0.2758583429396621</v>
+        <v>0.6761033155941802</v>
       </c>
       <c r="K15">
-        <v>1.95</v>
+        <v>2.54</v>
       </c>
       <c r="L15">
-        <v>0.03334185330602894</v>
+        <v>0.03689896535814968</v>
       </c>
       <c r="M15">
-        <v>177.8539978027344</v>
+        <v>88.78000030517578</v>
       </c>
       <c r="N15">
-        <v>172.8900001525879</v>
+        <v>84.6115005493164</v>
       </c>
       <c r="O15">
-        <v>157.3468008422851</v>
+        <v>80.17340042114257</v>
       </c>
       <c r="P15" t="b">
         <v>1</v>
       </c>
       <c r="Q15">
-        <v>135.4262498474121</v>
+        <v>67.67295000076294</v>
       </c>
       <c r="R15">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="S15">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="U15">
-        <v>4.444444444444444</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="V15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="b">
         <v>1</v>
@@ -2519,58 +2585,58 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>86.62</v>
+        <v>35.23</v>
       </c>
       <c r="Z15">
-        <v>183.3</v>
+        <v>92.61</v>
       </c>
       <c r="AA15">
-        <v>4375.62</v>
+        <v>19.21</v>
       </c>
       <c r="AB15">
-        <v>91.83</v>
+        <v>9.6</v>
       </c>
       <c r="AC15">
-        <v>45.8</v>
+        <v>18.13</v>
       </c>
       <c r="AD15">
-        <v>27.6</v>
+        <v>59.68</v>
       </c>
       <c r="AE15">
-        <v>115.46</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>70</v>
+        <v>40.27</v>
+      </c>
+      <c r="AF15">
+        <v>-30.5</v>
+      </c>
+      <c r="AG15">
+        <v>74.06999999999999</v>
+      </c>
+      <c r="AH15">
+        <v>17.39</v>
       </c>
       <c r="AI15" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AJ15" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AK15" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="AL15" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM15">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AN15">
-        <v>4.12</v>
+        <v>4.76</v>
       </c>
       <c r="AO15">
-        <v>32.9</v>
+        <v>25.26</v>
       </c>
       <c r="AP15">
-        <v>39.60576767971369</v>
+        <v>34.60299633079001</v>
       </c>
     </row>
     <row r="16" spans="1:42">
@@ -2578,124 +2644,124 @@
         <v>56</v>
       </c>
       <c r="B16">
-        <v>99.40357852882704</v>
+        <v>92.82868525896414</v>
       </c>
       <c r="C16">
-        <v>96.81908548707754</v>
+        <v>88.44621513944223</v>
       </c>
       <c r="D16">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="E16">
-        <v>185</v>
+        <v>96</v>
       </c>
       <c r="F16">
-        <v>112.15</v>
+        <v>248.65</v>
       </c>
       <c r="G16">
-        <v>1.768667034161844</v>
+        <v>0.3827226812680049</v>
       </c>
       <c r="H16">
-        <v>1.261123598530794</v>
+        <v>1.184834432382518</v>
       </c>
       <c r="I16">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="J16">
-        <v>-0.1273192352029208</v>
+        <v>-0.05055837166237909</v>
       </c>
       <c r="K16">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="L16">
-        <v>0.3772893926734877</v>
+        <v>-0.4533301458287011</v>
       </c>
       <c r="M16">
-        <v>109.9739990234375</v>
+        <v>249.3380035400391</v>
       </c>
       <c r="N16">
-        <v>105.9979995727539</v>
+        <v>245.868000793457</v>
       </c>
       <c r="O16">
-        <v>92.65639999389649</v>
+        <v>233.0214001464844</v>
       </c>
       <c r="P16" t="b">
         <v>1</v>
       </c>
       <c r="Q16">
-        <v>74.23514995574951</v>
+        <v>198.4118502807617</v>
       </c>
       <c r="R16">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="S16">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="U16">
-        <v>5.555555555555556</v>
+        <v>13.88888888888889</v>
       </c>
       <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="W16" t="b">
         <v>0</v>
       </c>
-      <c r="W16" t="b">
-        <v>1</v>
-      </c>
       <c r="X16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>35.23</v>
+        <v>150.2</v>
       </c>
       <c r="Z16">
-        <v>112.58</v>
+        <v>260.55</v>
       </c>
       <c r="AA16">
-        <v>23.29</v>
+        <v>265.16</v>
       </c>
       <c r="AB16">
-        <v>9.6</v>
+        <v>94.19</v>
       </c>
       <c r="AC16">
-        <v>18.47</v>
+        <v>21.06</v>
       </c>
       <c r="AD16">
-        <v>59.68</v>
+        <v>31.58</v>
       </c>
       <c r="AE16">
-        <v>40.27</v>
+        <v>28.09</v>
       </c>
       <c r="AF16">
-        <v>-30.5</v>
+        <v>5.11</v>
       </c>
       <c r="AG16">
-        <v>74.06999999999999</v>
+        <v>2.92</v>
       </c>
       <c r="AH16">
-        <v>17.39</v>
+        <v>47.41</v>
       </c>
       <c r="AI16" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AJ16" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="AL16" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM16">
-        <v>3.8</v>
+        <v>6.34</v>
       </c>
       <c r="AN16">
-        <v>4.76</v>
+        <v>5.24</v>
       </c>
       <c r="AO16">
-        <v>25.26</v>
+        <v>-17.35</v>
       </c>
       <c r="AP16">
-        <v>37.02165185411589</v>
+        <v>33.87717371223821</v>
       </c>
     </row>
     <row r="17" spans="1:42">
@@ -2703,124 +2769,124 @@
         <v>57</v>
       </c>
       <c r="B17">
-        <v>92.84294234592446</v>
+        <v>97.21115537848605</v>
       </c>
       <c r="C17">
-        <v>91.65009940357854</v>
+        <v>78.08764940239044</v>
       </c>
       <c r="D17">
-        <v>49</v>
+        <v>256</v>
       </c>
       <c r="E17">
-        <v>39</v>
+        <v>272</v>
       </c>
       <c r="F17">
-        <v>92.23</v>
+        <v>167.63</v>
       </c>
       <c r="G17">
-        <v>0.3579448800349937</v>
+        <v>0.6799300371268467</v>
       </c>
       <c r="H17">
-        <v>1.307343713790025</v>
+        <v>0.4381457035548194</v>
       </c>
       <c r="I17">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="J17">
-        <v>-0.4615322276105884</v>
+        <v>-0.6062408383879835</v>
       </c>
       <c r="K17">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="L17">
-        <v>-0.6709316796844812</v>
+        <v>-1.223690177693753</v>
       </c>
       <c r="M17">
-        <v>92.27200012207031</v>
+        <v>165.3879974365234</v>
       </c>
       <c r="N17">
-        <v>92.49449996948242</v>
+        <v>162.2334999084473</v>
       </c>
       <c r="O17">
-        <v>85.08019989013673</v>
+        <v>154.7795999145508</v>
       </c>
       <c r="P17" t="b">
         <v>1</v>
       </c>
       <c r="Q17">
-        <v>74.90460000991821</v>
+        <v>130.4315498733521</v>
       </c>
       <c r="R17">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="S17">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="U17">
-        <v>7.777777777777777</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="V17" t="b">
         <v>1</v>
       </c>
       <c r="W17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
       <c r="Y17">
-        <v>53.51</v>
+        <v>93.17</v>
       </c>
       <c r="Z17">
-        <v>96.91</v>
+        <v>168.44</v>
       </c>
       <c r="AA17">
-        <v>169.79</v>
+        <v>40.01</v>
       </c>
       <c r="AB17">
-        <v>-5.82</v>
+        <v>-5.3</v>
       </c>
       <c r="AC17">
-        <v>27.35</v>
+        <v>8.83</v>
       </c>
       <c r="AD17">
-        <v>28.46</v>
+        <v>99.37</v>
       </c>
       <c r="AE17">
-        <v>6.64</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>70</v>
+        <v>-26.76</v>
+      </c>
+      <c r="AF17">
+        <v>27.88</v>
+      </c>
+      <c r="AG17">
+        <v>-3.51</v>
+      </c>
+      <c r="AH17">
+        <v>78.12</v>
       </c>
       <c r="AI17" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AJ17" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AL17" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM17">
-        <v>6.77</v>
+        <v>6.38</v>
       </c>
       <c r="AN17">
-        <v>7.19</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AO17">
-        <v>6.2</v>
+        <v>35.42</v>
       </c>
       <c r="AP17">
-        <v>36.48807656663724</v>
+        <v>33.58058410305721</v>
       </c>
     </row>
     <row r="18" spans="1:42">
@@ -2828,124 +2894,124 @@
         <v>58</v>
       </c>
       <c r="B18">
-        <v>93.83697813121272</v>
+        <v>98.00796812749005</v>
       </c>
       <c r="C18">
-        <v>82.30616302186878</v>
+        <v>89.64143426294821</v>
       </c>
       <c r="D18">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="E18">
-        <v>173</v>
+        <v>238</v>
       </c>
       <c r="F18">
-        <v>102.29</v>
+        <v>1289.62</v>
       </c>
       <c r="G18">
-        <v>0.4561480142351148</v>
+        <v>0.767726060990229</v>
       </c>
       <c r="H18">
-        <v>0.9268455193475948</v>
+        <v>0.9647819338017315</v>
       </c>
       <c r="I18">
-        <v>0.99</v>
+        <v>1.43</v>
       </c>
       <c r="J18">
-        <v>-1.204227766294294</v>
+        <v>-0.5777443016328242</v>
       </c>
       <c r="K18">
+        <v>1.96</v>
+      </c>
+      <c r="L18">
+        <v>-0.6400840929475016</v>
+      </c>
+      <c r="M18">
+        <v>1300.878002929687</v>
+      </c>
+      <c r="N18">
+        <v>1257.9205078125</v>
+      </c>
+      <c r="O18">
+        <v>1203.724401855469</v>
+      </c>
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>960.4195980834961</v>
+      </c>
+      <c r="R18">
         <v>1.03</v>
-      </c>
-      <c r="L18">
-        <v>-1.473475938208551</v>
-      </c>
-      <c r="M18">
-        <v>101.1240005493164</v>
-      </c>
-      <c r="N18">
-        <v>98.92400016784669</v>
-      </c>
-      <c r="O18">
-        <v>93.78800018310547</v>
-      </c>
-      <c r="P18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18">
-        <v>84.51630012512207</v>
-      </c>
-      <c r="R18">
-        <v>1.02</v>
       </c>
       <c r="S18">
         <v>1.05</v>
       </c>
       <c r="U18">
-        <v>11.66666666666667</v>
+        <v>9.444444444444443</v>
       </c>
       <c r="V18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>60.93</v>
+        <v>587.04</v>
       </c>
       <c r="Z18">
-        <v>103.16</v>
+        <v>1341.15</v>
       </c>
       <c r="AA18">
-        <v>72.14</v>
+        <v>548.8200000000001</v>
       </c>
       <c r="AB18">
-        <v>5.14</v>
+        <v>36.85</v>
       </c>
       <c r="AC18">
-        <v>21.9</v>
+        <v>28.75</v>
       </c>
       <c r="AD18">
-        <v>27.03</v>
+        <v>25.26</v>
       </c>
       <c r="AE18">
-        <v>11.75</v>
+        <v>40.84</v>
       </c>
       <c r="AF18">
-        <v>1.92</v>
+        <v>54.69</v>
       </c>
       <c r="AG18">
-        <v>3.31</v>
+        <v>-20.83</v>
       </c>
       <c r="AH18">
-        <v>-1.31</v>
+        <v>10.62</v>
       </c>
       <c r="AI18" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AJ18" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="AK18" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AL18" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM18">
-        <v>6.54</v>
+        <v>21.14</v>
       </c>
       <c r="AN18">
-        <v>6.53</v>
+        <v>23.78</v>
       </c>
       <c r="AO18">
-        <v>-0.15</v>
+        <v>12.49</v>
       </c>
       <c r="AP18">
-        <v>35.9581870923122</v>
+        <v>32.49312861396719</v>
       </c>
     </row>
     <row r="19" spans="1:42">
@@ -2953,124 +3019,124 @@
         <v>59</v>
       </c>
       <c r="B19">
-        <v>96.22266401590457</v>
+        <v>91.43426294820716</v>
       </c>
       <c r="C19">
-        <v>99.40357852882704</v>
+        <v>79.68127490039841</v>
       </c>
       <c r="D19">
-        <v>46</v>
+        <v>215</v>
       </c>
       <c r="E19">
-        <v>71</v>
+        <v>210</v>
       </c>
       <c r="F19">
-        <v>138.78</v>
+        <v>90.55</v>
       </c>
       <c r="G19">
-        <v>0.3915713755461087</v>
+        <v>0.3937346344681577</v>
       </c>
       <c r="H19">
-        <v>1.763550984476286</v>
+        <v>0.860941781390585</v>
       </c>
       <c r="I19">
-        <v>4.26</v>
+        <v>0.8</v>
       </c>
       <c r="J19">
-        <v>2.843462919531902</v>
+        <v>-1.475385209420339</v>
       </c>
       <c r="K19">
-        <v>3.56</v>
+        <v>1.46</v>
       </c>
       <c r="L19">
-        <v>2.670272988456544</v>
+        <v>-1.223690177693753</v>
       </c>
       <c r="M19">
-        <v>123.6080001831055</v>
+        <v>89.7</v>
       </c>
       <c r="N19">
-        <v>115.0855007171631</v>
+        <v>87.52900047302246</v>
       </c>
       <c r="O19">
-        <v>103.3191998291016</v>
+        <v>83.14980010986328</v>
       </c>
       <c r="P19" t="b">
         <v>1</v>
       </c>
       <c r="Q19">
-        <v>98.72973728179932</v>
+        <v>78.56020034790039</v>
       </c>
       <c r="R19">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="S19">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="U19">
-        <v>3.888888888888888</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="V19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="b">
         <v>1</v>
       </c>
       <c r="X19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>59.43</v>
+        <v>59.95</v>
       </c>
       <c r="Z19">
-        <v>139.53</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="AA19">
-        <v>174.3</v>
+        <v>51.99</v>
       </c>
       <c r="AB19">
-        <v>27.37</v>
+        <v>4.53</v>
       </c>
       <c r="AC19">
-        <v>21.54</v>
+        <v>13.65</v>
       </c>
       <c r="AD19">
-        <v>34.62</v>
+        <v>68.48</v>
       </c>
       <c r="AE19">
-        <v>33.64</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>70</v>
+        <v>11.43</v>
+      </c>
+      <c r="AF19">
+        <v>13.11</v>
+      </c>
+      <c r="AG19">
+        <v>15.09</v>
+      </c>
+      <c r="AH19">
+        <v>35.9</v>
       </c>
       <c r="AI19" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="AJ19" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="AK19" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AL19" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM19">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="AN19">
-        <v>9.73</v>
+        <v>3.14</v>
       </c>
       <c r="AO19">
-        <v>310.55</v>
+        <v>42.08</v>
       </c>
       <c r="AP19">
-        <v>33.61126428705469</v>
+        <v>31.48360279428092</v>
       </c>
     </row>
     <row r="20" spans="1:42">
@@ -3078,124 +3144,124 @@
         <v>60</v>
       </c>
       <c r="B20">
-        <v>94.63220675944333</v>
+        <v>93.02788844621513</v>
       </c>
       <c r="C20">
-        <v>94.23459244532803</v>
+        <v>68.12749003984064</v>
       </c>
       <c r="D20">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="E20">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="F20">
-        <v>92.54000000000001</v>
+        <v>93.25</v>
       </c>
       <c r="G20">
-        <v>0.5593294081392726</v>
+        <v>0.4269476466629525</v>
       </c>
       <c r="H20">
-        <v>0.5360456227771172</v>
+        <v>0.8947871735122622</v>
       </c>
       <c r="I20">
-        <v>4.29</v>
+        <v>1.23</v>
       </c>
       <c r="J20">
-        <v>2.880597696466087</v>
+        <v>-0.8627096691844161</v>
       </c>
       <c r="K20">
-        <v>2.62</v>
+        <v>1.61</v>
       </c>
       <c r="L20">
-        <v>1.130698288430778</v>
+        <v>-1.048608352269877</v>
       </c>
       <c r="M20">
-        <v>92.03399963378907</v>
+        <v>91.90599975585937</v>
       </c>
       <c r="N20">
-        <v>82.14299964904785</v>
+        <v>90.66299934387207</v>
       </c>
       <c r="O20">
-        <v>78.44079971313477</v>
+        <v>87.9088003540039</v>
       </c>
       <c r="P20" t="b">
         <v>1</v>
       </c>
       <c r="Q20">
-        <v>68.80124994277953</v>
+        <v>81.69390007019042</v>
       </c>
       <c r="R20">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="S20">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="U20">
-        <v>2.222222222222222</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="V20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" t="b">
         <v>1</v>
       </c>
       <c r="X20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>54.55</v>
+        <v>59.19</v>
       </c>
       <c r="Z20">
-        <v>93.45999999999999</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="AA20">
-        <v>42.29</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="AB20">
-        <v>13.57</v>
+        <v>5.14</v>
       </c>
       <c r="AC20">
-        <v>11.61</v>
+        <v>17.28</v>
       </c>
       <c r="AD20">
-        <v>77.23</v>
+        <v>26.35</v>
       </c>
       <c r="AE20">
-        <v>42.63</v>
+        <v>11.29</v>
       </c>
       <c r="AF20">
-        <v>-21.74</v>
+        <v>1.92</v>
       </c>
       <c r="AG20">
-        <v>5.34</v>
+        <v>3.31</v>
       </c>
       <c r="AH20">
-        <v>191.11</v>
+        <v>-1.31</v>
       </c>
       <c r="AI20" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AJ20" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="AK20" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="AL20" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM20">
-        <v>4.5</v>
+        <v>6.13</v>
       </c>
       <c r="AN20">
-        <v>5.22</v>
+        <v>6.53</v>
       </c>
       <c r="AO20">
-        <v>16</v>
+        <v>6.53</v>
       </c>
       <c r="AP20">
-        <v>32.8476807468871</v>
+        <v>30.16544178205772</v>
       </c>
     </row>
     <row r="21" spans="1:42">
@@ -3203,61 +3269,64 @@
         <v>61</v>
       </c>
       <c r="B21">
-        <v>93.24055666003976</v>
+        <v>90.83665338645417</v>
       </c>
       <c r="C21">
-        <v>92.44532803180915</v>
+        <v>87.64940239043824</v>
       </c>
       <c r="D21">
-        <v>33</v>
+        <v>311</v>
       </c>
       <c r="E21">
-        <v>53</v>
+        <v>310</v>
       </c>
       <c r="F21">
-        <v>771.99</v>
+        <v>109.76</v>
       </c>
       <c r="G21">
-        <v>0.3200409834258302</v>
+        <v>0.3529597821390302</v>
       </c>
       <c r="H21">
-        <v>1.409922060668502</v>
+        <v>1.024511955313441</v>
       </c>
       <c r="I21">
-        <v>2.97</v>
+        <v>1.25</v>
       </c>
       <c r="J21">
-        <v>1.246667511361935</v>
+        <v>-0.8342131324292569</v>
       </c>
       <c r="K21">
-        <v>2.31</v>
+        <v>1.79</v>
       </c>
       <c r="L21">
-        <v>0.6229662065073864</v>
+        <v>-0.8385101617612268</v>
       </c>
       <c r="M21">
-        <v>767.05400390625</v>
+        <v>108.5719985961914</v>
       </c>
       <c r="N21">
-        <v>724.5804992675781</v>
+        <v>102.1570003509521</v>
       </c>
       <c r="O21">
-        <v>707.2640014648438</v>
+        <v>97.35099990844726</v>
       </c>
       <c r="P21" t="b">
         <v>1</v>
       </c>
       <c r="Q21">
-        <v>631.8972012329101</v>
+        <v>94.22944999694825</v>
       </c>
       <c r="R21">
         <v>1.06</v>
       </c>
       <c r="S21">
-        <v>1.02</v>
+        <v>1.05</v>
+      </c>
+      <c r="T21" t="s">
+        <v>74</v>
       </c>
       <c r="U21">
-        <v>3.888888888888888</v>
+        <v>8.888888888888888</v>
       </c>
       <c r="V21" t="b">
         <v>0</v>
@@ -3266,61 +3335,61 @@
         <v>1</v>
       </c>
       <c r="X21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>450.8</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="Z21">
-        <v>784.75</v>
+        <v>110.96</v>
       </c>
       <c r="AA21">
-        <v>1939.35</v>
+        <v>31.3</v>
       </c>
       <c r="AB21">
-        <v>29.99</v>
+        <v>8.85</v>
       </c>
       <c r="AC21">
-        <v>17.18</v>
+        <v>9.66</v>
       </c>
       <c r="AD21">
-        <v>38.3</v>
+        <v>49.27</v>
       </c>
       <c r="AE21">
-        <v>40.65</v>
+        <v>11.21</v>
       </c>
       <c r="AF21" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AG21" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH21" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AI21" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AJ21" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AL21" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM21">
-        <v>27.56</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AN21">
-        <v>25.3</v>
+        <v>9.34</v>
       </c>
       <c r="AO21">
-        <v>-8.199999999999999</v>
+        <v>5.18</v>
       </c>
       <c r="AP21">
-        <v>32.18670001250666</v>
+        <v>28.61158900061692</v>
       </c>
     </row>
     <row r="22" spans="1:42">
@@ -3328,124 +3397,124 @@
         <v>62</v>
       </c>
       <c r="B22">
-        <v>90.85487077534792</v>
+        <v>97.01195219123507</v>
       </c>
       <c r="C22">
-        <v>91.05367793240556</v>
+        <v>93.62549800796812</v>
       </c>
       <c r="D22">
-        <v>317</v>
+        <v>447</v>
       </c>
       <c r="E22">
-        <v>309</v>
+        <v>446</v>
       </c>
       <c r="F22">
-        <v>724.74</v>
+        <v>285.81</v>
       </c>
       <c r="G22">
-        <v>0.2779385420312903</v>
+        <v>0.5398638851734564</v>
       </c>
       <c r="H22">
-        <v>1.40082150343559</v>
+        <v>1.410675277480754</v>
       </c>
       <c r="I22">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="J22">
-        <v>-0.9071495508208119</v>
+        <v>-0.3070272024588117</v>
       </c>
       <c r="K22">
-        <v>1.38</v>
+        <v>2.71</v>
       </c>
       <c r="L22">
-        <v>-0.900230039262787</v>
+        <v>0.2353250341718749</v>
       </c>
       <c r="M22">
-        <v>720.9680053710938</v>
+        <v>277.3039978027344</v>
       </c>
       <c r="N22">
-        <v>715.8055023193359</v>
+        <v>271.5735000610351</v>
       </c>
       <c r="O22">
-        <v>674.0469995117187</v>
+        <v>263.6306005859375</v>
       </c>
       <c r="P22" t="b">
         <v>1</v>
       </c>
       <c r="Q22">
-        <v>601.2058996582032</v>
+        <v>234.3042502593994</v>
       </c>
       <c r="R22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="S22">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="U22">
-        <v>7.222222222222221</v>
+        <v>0</v>
       </c>
       <c r="V22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="b">
         <v>1</v>
       </c>
       <c r="X22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>437.37</v>
+        <v>155.96</v>
       </c>
       <c r="Z22">
-        <v>737.88</v>
+        <v>289.33</v>
       </c>
       <c r="AA22">
-        <v>219.39</v>
+        <v>17.31</v>
       </c>
       <c r="AB22">
-        <v>14.03</v>
+        <v>18.45</v>
       </c>
       <c r="AC22">
-        <v>14.57</v>
+        <v>11.89</v>
       </c>
       <c r="AD22">
-        <v>26.62</v>
+        <v>46.25</v>
       </c>
       <c r="AE22">
-        <v>12.78</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>70</v>
+        <v>29.49</v>
+      </c>
+      <c r="AF22">
+        <v>-56.51</v>
+      </c>
+      <c r="AG22">
+        <v>101.69</v>
+      </c>
+      <c r="AH22">
+        <v>-11.61</v>
       </c>
       <c r="AI22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AK22" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="AL22" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM22">
-        <v>45.42</v>
+        <v>11.61</v>
       </c>
       <c r="AN22">
-        <v>41.56</v>
+        <v>13.02</v>
       </c>
       <c r="AO22">
-        <v>-8.5</v>
+        <v>12.14</v>
       </c>
       <c r="AP22">
-        <v>29.66956586435544</v>
+        <v>25.02754800744032</v>
       </c>
     </row>
     <row r="23" spans="1:42">
@@ -3453,61 +3522,61 @@
         <v>63</v>
       </c>
       <c r="B23">
-        <v>96.42147117296223</v>
+        <v>97.80876494023904</v>
       </c>
       <c r="C23">
-        <v>85.08946322067594</v>
+        <v>59.56175298804781</v>
       </c>
       <c r="D23">
-        <v>466</v>
+        <v>143</v>
       </c>
       <c r="E23">
-        <v>472</v>
+        <v>141</v>
       </c>
       <c r="F23">
-        <v>302.96</v>
+        <v>181.2</v>
       </c>
       <c r="G23">
-        <v>0.589218574912048</v>
+        <v>0.7446734671786887</v>
       </c>
       <c r="H23">
-        <v>1.430313003578552</v>
+        <v>0.1256578853158136</v>
       </c>
       <c r="I23">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="J23">
-        <v>-0.7833669610401942</v>
+        <v>-0.8769579375619957</v>
       </c>
       <c r="K23">
-        <v>1.72</v>
+        <v>1.23</v>
       </c>
       <c r="L23">
-        <v>-0.343362594572616</v>
+        <v>-1.492148976677028</v>
       </c>
       <c r="M23">
-        <v>299.8339965820313</v>
+        <v>179.1300018310547</v>
       </c>
       <c r="N23">
-        <v>294.1114974975586</v>
+        <v>181.6110008239746</v>
       </c>
       <c r="O23">
-        <v>282.4965991210938</v>
+        <v>176.8078002929688</v>
       </c>
       <c r="P23" t="b">
         <v>1</v>
       </c>
       <c r="Q23">
-        <v>245.282850112915</v>
+        <v>145.724100227356</v>
       </c>
       <c r="R23">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="S23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="V23" t="b">
         <v>1</v>
@@ -3516,61 +3585,61 @@
         <v>1</v>
       </c>
       <c r="X23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>155.96</v>
+        <v>100.8</v>
       </c>
       <c r="Z23">
-        <v>306.34</v>
+        <v>186.69</v>
       </c>
       <c r="AA23">
-        <v>18.35</v>
+        <v>282.04</v>
       </c>
       <c r="AB23">
-        <v>18.45</v>
+        <v>-0.38</v>
       </c>
       <c r="AC23">
-        <v>13.59</v>
+        <v>13.64</v>
       </c>
       <c r="AD23">
-        <v>46.25</v>
+        <v>25.05</v>
       </c>
       <c r="AE23">
-        <v>29.49</v>
+        <v>-31.78</v>
       </c>
       <c r="AF23">
-        <v>-56.51</v>
+        <v>564.86</v>
       </c>
       <c r="AG23">
-        <v>101.69</v>
+        <v>-118.69</v>
       </c>
       <c r="AH23">
-        <v>-11.61</v>
+        <v>28.57</v>
       </c>
       <c r="AI23" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AJ23" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="AL23" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM23">
-        <v>11.61</v>
+        <v>6.35</v>
       </c>
       <c r="AN23">
-        <v>13.02</v>
+        <v>7.2</v>
       </c>
       <c r="AO23">
-        <v>12.14</v>
+        <v>13.39</v>
       </c>
       <c r="AP23">
-        <v>29.36148591768099</v>
+        <v>24.05595717302313</v>
       </c>
     </row>
     <row r="24" spans="1:42">
@@ -3578,61 +3647,61 @@
         <v>64</v>
       </c>
       <c r="B24">
-        <v>95.42743538767395</v>
+        <v>93.82470119521913</v>
       </c>
       <c r="C24">
-        <v>81.51093439363817</v>
+        <v>94.22310756972112</v>
       </c>
       <c r="D24">
-        <v>449</v>
+        <v>383</v>
       </c>
       <c r="E24">
-        <v>476</v>
+        <v>393</v>
       </c>
       <c r="F24">
-        <v>321.23</v>
+        <v>385.8</v>
       </c>
       <c r="G24">
-        <v>0.4862574799228668</v>
+        <v>0.3608236866456403</v>
       </c>
       <c r="H24">
-        <v>1.035389055916581</v>
+        <v>1.308396478463043</v>
       </c>
       <c r="I24">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="J24">
-        <v>-0.1149409762248591</v>
+        <v>-0.72022698540862</v>
       </c>
       <c r="K24">
-        <v>1.42</v>
+        <v>2.41</v>
       </c>
       <c r="L24">
-        <v>-0.8347162222404139</v>
+        <v>-0.1148386166758755</v>
       </c>
       <c r="M24">
-        <v>316.3720031738281</v>
+        <v>379.2179992675781</v>
       </c>
       <c r="N24">
-        <v>302.6950012207031</v>
+        <v>367.4500015258789</v>
       </c>
       <c r="O24">
-        <v>296.4492004394531</v>
+        <v>344.8133990478516</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
       </c>
       <c r="Q24">
-        <v>272.118900756836</v>
+        <v>311.2908502197266</v>
       </c>
       <c r="R24">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="S24">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="V24" t="b">
         <v>0</v>
@@ -3641,61 +3710,61 @@
         <v>1</v>
       </c>
       <c r="X24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>184.81</v>
+        <v>227.08</v>
       </c>
       <c r="Z24">
-        <v>334</v>
+        <v>388</v>
       </c>
       <c r="AA24">
-        <v>18.59</v>
+        <v>57.18</v>
       </c>
       <c r="AB24">
+        <v>17.22</v>
+      </c>
+      <c r="AC24">
+        <v>15.19</v>
+      </c>
+      <c r="AD24">
+        <v>20.58</v>
+      </c>
+      <c r="AE24">
+        <v>13.48</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>91</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM24">
         <v>6.18</v>
       </c>
-      <c r="AC24">
-        <v>15.14</v>
-      </c>
-      <c r="AD24">
-        <v>33.42</v>
-      </c>
-      <c r="AE24">
-        <v>20.58</v>
-      </c>
-      <c r="AF24">
-        <v>-11.93</v>
-      </c>
-      <c r="AG24">
-        <v>0.71</v>
-      </c>
-      <c r="AH24">
-        <v>15.04</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>71</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK24" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL24" t="s">
-        <v>107</v>
-      </c>
-      <c r="AM24">
-        <v>11.35</v>
-      </c>
       <c r="AN24">
-        <v>15.4</v>
+        <v>10.16</v>
       </c>
       <c r="AO24">
-        <v>35.68</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AP24">
-        <v>27.9830745742196</v>
+        <v>24.00561856157574</v>
       </c>
     </row>
     <row r="25" spans="1:42">
@@ -3703,124 +3772,124 @@
         <v>65</v>
       </c>
       <c r="B25">
-        <v>93.63817097415506</v>
+        <v>92.43027888446214</v>
       </c>
       <c r="C25">
-        <v>81.31212723658051</v>
+        <v>92.62948207171314</v>
       </c>
       <c r="D25">
-        <v>367</v>
+        <v>213</v>
       </c>
       <c r="E25">
-        <v>397</v>
+        <v>285</v>
       </c>
       <c r="F25">
-        <v>387.5</v>
+        <v>710.9299999999999</v>
       </c>
       <c r="G25">
-        <v>0.3442646510353168</v>
+        <v>0.3580753948281624</v>
       </c>
       <c r="H25">
-        <v>1.257104313757708</v>
+        <v>1.379558424999357</v>
       </c>
       <c r="I25">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="J25">
-        <v>-0.486288745566712</v>
+        <v>-0.8057165956740976</v>
       </c>
       <c r="K25">
-        <v>1.49</v>
+        <v>2.19</v>
       </c>
       <c r="L25">
-        <v>-0.720067042451261</v>
+        <v>-0.3716252939642262</v>
       </c>
       <c r="M25">
-        <v>394.3080017089844</v>
+        <v>712.9420043945313</v>
       </c>
       <c r="N25">
-        <v>398.0484970092774</v>
+        <v>657.7639953613282</v>
       </c>
       <c r="O25">
-        <v>377.1065985107422</v>
+        <v>613.7959973144531</v>
       </c>
       <c r="P25" t="b">
         <v>1</v>
       </c>
       <c r="Q25">
-        <v>322.0022998046875</v>
+        <v>577.6768492126465</v>
       </c>
       <c r="R25">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="S25">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="U25">
-        <v>3.333333333333333</v>
+        <v>7.222222222222221</v>
       </c>
       <c r="V25" t="b">
         <v>0</v>
       </c>
       <c r="W25" t="b">
+        <v>1</v>
+      </c>
+      <c r="X25" t="b">
         <v>0</v>
       </c>
-      <c r="X25" t="b">
-        <v>1</v>
-      </c>
       <c r="Y25">
-        <v>227.08</v>
+        <v>437.37</v>
       </c>
       <c r="Z25">
-        <v>424.94</v>
+        <v>726</v>
       </c>
       <c r="AA25">
-        <v>57.74</v>
+        <v>218.14</v>
       </c>
       <c r="AB25">
-        <v>17.22</v>
+        <v>14.03</v>
       </c>
       <c r="AC25">
-        <v>17.59</v>
+        <v>10.37</v>
       </c>
       <c r="AD25">
-        <v>20.92</v>
+        <v>21.98</v>
       </c>
       <c r="AE25">
-        <v>13.47</v>
+        <v>12.26</v>
       </c>
       <c r="AF25" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AG25" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH25" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AJ25" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="AL25" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM25">
-        <v>6.46</v>
+        <v>43.06</v>
       </c>
       <c r="AN25">
-        <v>10.16</v>
+        <v>41.56</v>
       </c>
       <c r="AO25">
-        <v>57.28</v>
+        <v>-3.48</v>
       </c>
       <c r="AP25">
-        <v>27.70907854279514</v>
+        <v>23.87881481718585</v>
       </c>
     </row>
     <row r="26" spans="1:42">
@@ -3828,61 +3897,61 @@
         <v>66</v>
       </c>
       <c r="B26">
-        <v>92.6441351888668</v>
+        <v>97.41035856573706</v>
       </c>
       <c r="C26">
-        <v>73.558648111332</v>
+        <v>64.14342629482071</v>
       </c>
       <c r="D26">
-        <v>235</v>
+        <v>474</v>
       </c>
       <c r="E26">
-        <v>184</v>
+        <v>484</v>
       </c>
       <c r="F26">
-        <v>212.88</v>
+        <v>299.26</v>
       </c>
       <c r="G26">
-        <v>0.2939023205235858</v>
+        <v>0.6288469830830771</v>
       </c>
       <c r="H26">
-        <v>1.530051069852592</v>
+        <v>1.013623062756025</v>
       </c>
       <c r="I26">
-        <v>1.48</v>
+        <v>1.15</v>
       </c>
       <c r="J26">
-        <v>-0.5976930763692679</v>
+        <v>-0.9766958162050529</v>
       </c>
       <c r="K26">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="L26">
-        <v>-0.2614703232946496</v>
+        <v>-0.8034937966764518</v>
       </c>
       <c r="M26">
-        <v>211.6279998779297</v>
+        <v>297.1600036621094</v>
       </c>
       <c r="N26">
-        <v>215.3959999084473</v>
+        <v>293.1780014038086</v>
       </c>
       <c r="O26">
-        <v>207.5605993652344</v>
+        <v>284.201401977539</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
       </c>
       <c r="Q26">
-        <v>188.8754996490478</v>
+        <v>262.9355506134033</v>
       </c>
       <c r="R26">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="S26">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="U26">
-        <v>3.888888888888888</v>
+        <v>0</v>
       </c>
       <c r="V26" t="b">
         <v>1</v>
@@ -3894,58 +3963,58 @@
         <v>1</v>
       </c>
       <c r="Y26">
-        <v>128.23</v>
+        <v>169.55</v>
       </c>
       <c r="Z26">
-        <v>232.45</v>
+        <v>313</v>
       </c>
       <c r="AA26">
-        <v>136.14</v>
+        <v>17.19</v>
       </c>
       <c r="AB26">
-        <v>0.96</v>
+        <v>6.18</v>
       </c>
       <c r="AC26">
-        <v>23.15</v>
+        <v>9.25</v>
       </c>
       <c r="AD26">
-        <v>10.24</v>
+        <v>23.97</v>
       </c>
       <c r="AE26">
-        <v>7.9</v>
+        <v>19.89</v>
       </c>
       <c r="AF26">
-        <v>30.08</v>
+        <v>-11.93</v>
       </c>
       <c r="AG26">
-        <v>-39.82</v>
+        <v>0.71</v>
       </c>
       <c r="AH26">
-        <v>217.99</v>
+        <v>15.04</v>
       </c>
       <c r="AI26" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AJ26" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="AL26" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM26">
-        <v>0.36</v>
+        <v>10.53</v>
       </c>
       <c r="AN26">
-        <v>15.66</v>
+        <v>15.4</v>
       </c>
       <c r="AO26">
-        <v>4250</v>
+        <v>46.25</v>
       </c>
       <c r="AP26">
-        <v>25.58105599505063</v>
+        <v>19.897606617552</v>
       </c>
     </row>
     <row r="27" spans="1:42">
@@ -3953,124 +4022,124 @@
         <v>67</v>
       </c>
       <c r="B27">
-        <v>92.04771371769384</v>
+        <v>97.60956175298804</v>
       </c>
       <c r="C27">
-        <v>78.13121272365805</v>
+        <v>57.96812749003985</v>
       </c>
       <c r="D27">
-        <v>470</v>
+        <v>148</v>
       </c>
       <c r="E27">
-        <v>454</v>
+        <v>176</v>
       </c>
       <c r="F27">
-        <v>141.23</v>
+        <v>106.65</v>
       </c>
       <c r="G27">
-        <v>0.4048815553017485</v>
+        <v>0.6256772002030457</v>
       </c>
       <c r="H27">
-        <v>0.8199613997192428</v>
+        <v>1.055766488718523</v>
       </c>
       <c r="I27">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="J27">
-        <v>0.4792154547221055</v>
+        <v>-0.1075514451726975</v>
       </c>
       <c r="K27">
-        <v>1.73</v>
+        <v>2.74</v>
       </c>
       <c r="L27">
-        <v>-0.3269841403170227</v>
+        <v>0.2703413992566503</v>
       </c>
       <c r="M27">
-        <v>139.5579986572266</v>
+        <v>104.534001159668</v>
       </c>
       <c r="N27">
-        <v>129.5065002441406</v>
+        <v>102.9780002593994</v>
       </c>
       <c r="O27">
-        <v>124.5491999816895</v>
+        <v>103.2192002868652</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
       </c>
       <c r="Q27">
-        <v>119.0526998901367</v>
+        <v>96.06950023651123</v>
       </c>
       <c r="R27">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="S27">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="U27">
         <v>0</v>
       </c>
       <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="W27" t="b">
+        <v>1</v>
+      </c>
+      <c r="X27" t="b">
         <v>0</v>
       </c>
-      <c r="W27" t="b">
-        <v>1</v>
-      </c>
-      <c r="X27" t="b">
-        <v>1</v>
-      </c>
       <c r="Y27">
-        <v>86.09999999999999</v>
+        <v>54.57</v>
       </c>
       <c r="Z27">
-        <v>144</v>
+        <v>114.82</v>
       </c>
       <c r="AA27">
-        <v>11.66</v>
+        <v>81.63</v>
       </c>
       <c r="AB27">
-        <v>11.82</v>
+        <v>42.92</v>
       </c>
       <c r="AC27">
-        <v>15.63</v>
+        <v>4.31</v>
       </c>
       <c r="AD27">
-        <v>7.95</v>
+        <v>43.64</v>
       </c>
       <c r="AE27">
-        <v>20.47</v>
+        <v>205.91</v>
       </c>
       <c r="AF27">
-        <v>1.67</v>
+        <v>-17.65</v>
       </c>
       <c r="AG27">
-        <v>-13.04</v>
+        <v>-4.23</v>
       </c>
       <c r="AH27">
-        <v>21.91</v>
+        <v>42</v>
       </c>
       <c r="AI27" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ27" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="AL27" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM27">
-        <v>12.5</v>
+        <v>2.43</v>
       </c>
       <c r="AN27">
-        <v>13.55</v>
+        <v>2.41</v>
       </c>
       <c r="AO27">
-        <v>8.4</v>
+        <v>-0.82</v>
       </c>
       <c r="AP27">
-        <v>18.09429331421221</v>
+        <v>18.50453200046875</v>
       </c>
     </row>
     <row r="28" spans="1:42">
@@ -4078,58 +4147,58 @@
         <v>68</v>
       </c>
       <c r="B28">
-        <v>97.01789264413519</v>
+        <v>95.2191235059761</v>
       </c>
       <c r="C28">
-        <v>100</v>
+        <v>98.80478087649402</v>
       </c>
       <c r="D28">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="E28">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="F28">
-        <v>256.43</v>
+        <v>232.26</v>
       </c>
       <c r="G28">
-        <v>0.691948430557189</v>
+        <v>0.4406656914781227</v>
       </c>
       <c r="H28">
-        <v>1.466262117550942</v>
+        <v>1.450397037248662</v>
       </c>
       <c r="I28">
-        <v>1.83</v>
+        <v>3.87</v>
       </c>
       <c r="J28">
-        <v>-0.1644540121371062</v>
+        <v>2.898833182496597</v>
       </c>
       <c r="K28">
-        <v>2.67</v>
+        <v>3.22</v>
       </c>
       <c r="L28">
-        <v>1.212590559708744</v>
+        <v>0.8306032406130512</v>
       </c>
       <c r="M28">
-        <v>252.5639984130859</v>
+        <v>227.4300018310547</v>
       </c>
       <c r="N28">
-        <v>244.395499420166</v>
+        <v>207.4335006713867</v>
       </c>
       <c r="O28">
-        <v>216.7206002807617</v>
+        <v>176.2283999633789</v>
       </c>
       <c r="P28" t="b">
         <v>1</v>
       </c>
       <c r="Q28">
-        <v>176.7721500396729</v>
+        <v>168.7022501373291</v>
       </c>
       <c r="R28">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="S28">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="U28">
         <v>3.333333333333333</v>
@@ -4147,10 +4216,10 @@
         <v>118.86</v>
       </c>
       <c r="Z28">
-        <v>260.87</v>
+        <v>237.99</v>
       </c>
       <c r="AA28">
-        <v>720.27</v>
+        <v>652.38</v>
       </c>
       <c r="AB28">
         <v>7.13</v>
@@ -4165,37 +4234,37 @@
         <v>85.36</v>
       </c>
       <c r="AF28" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AG28" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH28" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="AJ28" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="AL28" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="AM28">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="AN28">
         <v>7.16</v>
       </c>
       <c r="AO28">
-        <v>64.59999999999999</v>
+        <v>64.98</v>
       </c>
       <c r="AP28">
-        <v>17.44605741971345</v>
+        <v>17.67876153523423</v>
       </c>
     </row>
     <row r="29" spans="1:42">
@@ -4203,61 +4272,61 @@
         <v>69</v>
       </c>
       <c r="B29">
-        <v>94.83101391650099</v>
+        <v>95.4183266932271</v>
       </c>
       <c r="C29">
-        <v>86.28230616302187</v>
+        <v>61.15537848605578</v>
       </c>
       <c r="D29">
-        <v>306</v>
+        <v>446</v>
       </c>
       <c r="E29">
-        <v>321</v>
+        <v>454</v>
       </c>
       <c r="F29">
-        <v>84.13</v>
+        <v>287.49</v>
       </c>
       <c r="G29">
-        <v>0.3951068368871127</v>
+        <v>0.5644441392536974</v>
       </c>
       <c r="H29">
-        <v>1.362694310556965</v>
+        <v>0.4639218687611283</v>
       </c>
       <c r="I29">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="J29">
-        <v>-0.8947712918427502</v>
+        <v>-0.9481992794498937</v>
       </c>
       <c r="K29">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="L29">
-        <v>-1.293312941397025</v>
+        <v>-1.013591987185102</v>
       </c>
       <c r="M29">
-        <v>83.52199859619141</v>
+        <v>286.7419921875</v>
       </c>
       <c r="N29">
-        <v>82.73899955749512</v>
+        <v>283.3409957885742</v>
       </c>
       <c r="O29">
-        <v>77.32019989013672</v>
+        <v>280.0145983886719</v>
       </c>
       <c r="P29" t="b">
         <v>1</v>
       </c>
       <c r="Q29">
-        <v>71.06234996795655</v>
+        <v>227.3475998687744</v>
       </c>
       <c r="R29">
         <v>1.01</v>
       </c>
       <c r="S29">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="U29">
-        <v>11.66666666666667</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="V29" t="b">
         <v>1</v>
@@ -4269,58 +4338,436 @@
         <v>0</v>
       </c>
       <c r="Y29">
-        <v>48.65</v>
+        <v>172.49</v>
       </c>
       <c r="Z29">
-        <v>87.5</v>
+        <v>290.38</v>
       </c>
       <c r="AA29">
-        <v>20.07</v>
+        <v>27</v>
       </c>
       <c r="AB29">
-        <v>24.51</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AC29">
-        <v>1.84</v>
+        <v>9.82</v>
       </c>
       <c r="AD29">
-        <v>17.17</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="AE29">
-        <v>31</v>
-      </c>
-      <c r="AF29" t="s">
+        <v>-10.08</v>
+      </c>
+      <c r="AF29">
+        <v>5.5</v>
+      </c>
+      <c r="AG29">
+        <v>-3.38</v>
+      </c>
+      <c r="AH29">
+        <v>2.99</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM29">
+        <v>8.19</v>
+      </c>
+      <c r="AN29">
+        <v>8.65</v>
+      </c>
+      <c r="AO29">
+        <v>5.62</v>
+      </c>
+      <c r="AP29">
+        <v>17.08501491553235</v>
+      </c>
+    </row>
+    <row r="30" spans="1:42">
+      <c r="A30" t="s">
         <v>70</v>
       </c>
-      <c r="AG29" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH29" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI29" t="s">
-        <v>70</v>
-      </c>
-      <c r="AJ29" t="s">
+      <c r="B30">
+        <v>91.03585657370517</v>
+      </c>
+      <c r="C30">
+        <v>55.77689243027888</v>
+      </c>
+      <c r="D30">
+        <v>201</v>
+      </c>
+      <c r="E30">
+        <v>236</v>
+      </c>
+      <c r="F30">
+        <v>151.84</v>
+      </c>
+      <c r="G30">
+        <v>0.3631447281168498</v>
+      </c>
+      <c r="H30">
+        <v>1.061995651886762</v>
+      </c>
+      <c r="I30">
+        <v>1.35</v>
+      </c>
+      <c r="J30">
+        <v>-0.6917304486534608</v>
+      </c>
+      <c r="K30">
+        <v>2.26</v>
+      </c>
+      <c r="L30">
+        <v>-0.2899204420997512</v>
+      </c>
+      <c r="M30">
+        <v>152.9600006103516</v>
+      </c>
+      <c r="N30">
+        <v>147.7840003967285</v>
+      </c>
+      <c r="O30">
+        <v>146.3576007080078</v>
+      </c>
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30">
+        <v>140.2076499176025</v>
+      </c>
+      <c r="R30">
+        <v>1.04</v>
+      </c>
+      <c r="S30">
+        <v>1.01</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+      <c r="W30" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>98.26000000000001</v>
+      </c>
+      <c r="Z30">
+        <v>156.35</v>
+      </c>
+      <c r="AA30">
+        <v>81.72</v>
+      </c>
+      <c r="AB30">
+        <v>-0.67</v>
+      </c>
+      <c r="AC30">
+        <v>5.33</v>
+      </c>
+      <c r="AD30">
+        <v>22.06</v>
+      </c>
+      <c r="AE30">
+        <v>94.75</v>
+      </c>
+      <c r="AF30">
+        <v>51.85</v>
+      </c>
+      <c r="AG30">
+        <v>-45.78</v>
+      </c>
+      <c r="AH30">
+        <v>20.29</v>
+      </c>
+      <c r="AI30" t="s">
         <v>87</v>
       </c>
-      <c r="AK29" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL29" t="s">
-        <v>107</v>
-      </c>
-      <c r="AM29">
-        <v>6.13</v>
-      </c>
-      <c r="AN29">
-        <v>2.98</v>
-      </c>
-      <c r="AO29">
-        <v>-51.39</v>
-      </c>
-      <c r="AP29">
-        <v>11.6238758500156</v>
+      <c r="AJ30" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>125</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM30">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="AN30">
+        <v>7.9</v>
+      </c>
+      <c r="AO30">
+        <v>-1.62</v>
+      </c>
+      <c r="AP30">
+        <v>16.08340190940222</v>
+      </c>
+    </row>
+    <row r="31" spans="1:42">
+      <c r="A31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31">
+        <v>93.62549800796812</v>
+      </c>
+      <c r="C31">
+        <v>85.4581673306773</v>
+      </c>
+      <c r="D31">
+        <v>163</v>
+      </c>
+      <c r="E31">
+        <v>189</v>
+      </c>
+      <c r="F31">
+        <v>218.13</v>
+      </c>
+      <c r="G31">
+        <v>0.4051654545433332</v>
+      </c>
+      <c r="H31">
+        <v>1.478614638909965</v>
+      </c>
+      <c r="I31">
+        <v>1.48</v>
+      </c>
+      <c r="J31">
+        <v>-0.5065029597449262</v>
+      </c>
+      <c r="K31">
+        <v>2.85</v>
+      </c>
+      <c r="L31">
+        <v>0.3987347379008254</v>
+      </c>
+      <c r="M31">
+        <v>217.1579986572266</v>
+      </c>
+      <c r="N31">
+        <v>204.9794982910156</v>
+      </c>
+      <c r="O31">
+        <v>196.0235992431641</v>
+      </c>
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31">
+        <v>181.7124996948242</v>
+      </c>
+      <c r="R31">
+        <v>1.06</v>
+      </c>
+      <c r="S31">
+        <v>1.05</v>
+      </c>
+      <c r="T31" t="s">
+        <v>74</v>
+      </c>
+      <c r="U31">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="V31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" t="b">
+        <v>1</v>
+      </c>
+      <c r="X31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y31">
+        <v>128.23</v>
+      </c>
+      <c r="Z31">
+        <v>221.95</v>
+      </c>
+      <c r="AA31">
+        <v>139.52</v>
+      </c>
+      <c r="AB31">
+        <v>0.96</v>
+      </c>
+      <c r="AC31">
+        <v>6.23</v>
+      </c>
+      <c r="AD31">
+        <v>10.24</v>
+      </c>
+      <c r="AE31">
+        <v>7.9</v>
+      </c>
+      <c r="AF31">
+        <v>30.08</v>
+      </c>
+      <c r="AG31">
+        <v>-39.82</v>
+      </c>
+      <c r="AH31">
+        <v>217.99</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>103</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM31">
+        <v>11.91</v>
+      </c>
+      <c r="AN31">
+        <v>15.66</v>
+      </c>
+      <c r="AO31">
+        <v>31.49</v>
+      </c>
+      <c r="AP31">
+        <v>13.61316225703201</v>
+      </c>
+    </row>
+    <row r="32" spans="1:42">
+      <c r="A32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32">
+        <v>90.2390438247012</v>
+      </c>
+      <c r="C32">
+        <v>48.60557768924303</v>
+      </c>
+      <c r="D32">
+        <v>377</v>
+      </c>
+      <c r="E32">
+        <v>341</v>
+      </c>
+      <c r="F32">
+        <v>216.02</v>
+      </c>
+      <c r="G32">
+        <v>0.390575318108716</v>
+      </c>
+      <c r="H32">
+        <v>0.6822364596992659</v>
+      </c>
+      <c r="I32">
+        <v>1.28</v>
+      </c>
+      <c r="J32">
+        <v>-0.7914683272965181</v>
+      </c>
+      <c r="K32">
+        <v>1.52</v>
+      </c>
+      <c r="L32">
+        <v>-1.153657447524203</v>
+      </c>
+      <c r="M32">
+        <v>218.6380035400391</v>
+      </c>
+      <c r="N32">
+        <v>219.4700004577637</v>
+      </c>
+      <c r="O32">
+        <v>211.4788006591797</v>
+      </c>
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32">
+        <v>188.6509003448486</v>
+      </c>
+      <c r="R32">
+        <v>1</v>
+      </c>
+      <c r="S32">
+        <v>1.04</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32" t="b">
+        <v>1</v>
+      </c>
+      <c r="W32" t="b">
+        <v>0</v>
+      </c>
+      <c r="X32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y32">
+        <v>135.87</v>
+      </c>
+      <c r="Z32">
+        <v>228.27</v>
+      </c>
+      <c r="AA32">
+        <v>25.28</v>
+      </c>
+      <c r="AB32">
+        <v>110.48</v>
+      </c>
+      <c r="AC32">
+        <v>11.88</v>
+      </c>
+      <c r="AD32">
+        <v>0.57</v>
+      </c>
+      <c r="AE32">
+        <v>46.16</v>
+      </c>
+      <c r="AF32">
+        <v>50.82</v>
+      </c>
+      <c r="AG32">
+        <v>4.57</v>
+      </c>
+      <c r="AH32">
+        <v>-31.91</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>97</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>127</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM32">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="AN32">
+        <v>10.56</v>
+      </c>
+      <c r="AO32">
+        <v>18.92</v>
+      </c>
+      <c r="AP32">
+        <v>6.203481414216847</v>
       </c>
     </row>
   </sheetData>
